--- a/AAII_Financials/Yearly/CLWT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CLWT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>CLWT</t>
   </si>
@@ -905,8 +905,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>4100</v>
       </c>
       <c r="E12" s="3">
         <v>3600</v>
@@ -2267,7 +2267,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="E43" s="3">
         <v>1600</v>
@@ -2368,8 +2368,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -3023,7 +3023,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
@@ -4090,7 +4090,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
